--- a/Assets/04. Bakery Factory/ItemData.xlsx
+++ b/Assets/04. Bakery Factory/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3B506D-A224-4D00-AD56-331ECF471734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDCBC66-4081-41FF-A8ED-91367AEEB44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7785" yWindow="1365" windowWidth="28800" windowHeight="15435" xr2:uid="{FA01C06C-13EC-4B2C-B216-770647FE3958}"/>
+    <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{FA01C06C-13EC-4B2C-B216-770647FE3958}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>ItemName</t>
   </si>
@@ -125,6 +125,47 @@
   </si>
   <si>
     <t>ProUp</t>
+  </si>
+  <si>
+    <t>모루 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모루를 강화합니다.
+강화 단계 한도가 4만큼 증가하고
+무기 강화 확률이 1%p 상승합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnhancecAnvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeAnvil</t>
+  </si>
+  <si>
+    <t>500만(최초)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해머 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망치를 강화합니다.
+강화 성공확률이 5% 상승합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnhanceHammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>700만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeHammer</t>
   </si>
 </sst>
 </file>
@@ -170,9 +211,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,10 +532,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B500EC6A-A8F3-4551-A746-C98FD2D2177C}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="23.25" customWidth="1"/>
     <col min="2" max="2" width="33.75" customWidth="1"/>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
@@ -612,10 +656,56 @@
         <v>19</v>
       </c>
     </row>
+    <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6">
+        <v>5000000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7">
+        <v>7000000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C5" xr:uid="{9F8A1CA2-7F49-4A75-B45F-16D03AE7A658}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C7" xr:uid="{9F8A1CA2-7F49-4A75-B45F-16D03AE7A658}">
       <formula1>"true, false"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/04. Bakery Factory/ItemData.xlsx
+++ b/Assets/04. Bakery Factory/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDCBC66-4081-41FF-A8ED-91367AEEB44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15417D22-6CEC-4DA8-B22C-093AA8B0945E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{FA01C06C-13EC-4B2C-B216-770647FE3958}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>ItemName</t>
   </si>
@@ -166,6 +166,26 @@
   </si>
   <si>
     <t>UpgradeHammer</t>
+  </si>
+  <si>
+    <t>골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고를 보고 골드를 획득합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdsGold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO : 획득할 골드 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -532,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B500EC6A-A8F3-4551-A746-C98FD2D2177C}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.25" customWidth="1"/>
@@ -541,7 +561,7 @@
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="10.875" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
-    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -702,10 +722,33 @@
         <v>34</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C7" xr:uid="{9F8A1CA2-7F49-4A75-B45F-16D03AE7A658}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C8" xr:uid="{9F8A1CA2-7F49-4A75-B45F-16D03AE7A658}">
       <formula1>"true, false"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/04. Bakery Factory/ItemData.xlsx
+++ b/Assets/04. Bakery Factory/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15417D22-6CEC-4DA8-B22C-093AA8B0945E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2FDCB8-A8AC-414A-9A95-E2CA467E5770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{FA01C06C-13EC-4B2C-B216-770647FE3958}"/>
   </bookViews>
@@ -168,10 +168,6 @@
     <t>UpgradeHammer</t>
   </si>
   <si>
-    <t>골드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>광고를 보고 골드를 획득합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -185,6 +181,10 @@
   </si>
   <si>
     <t>TODO : 획득할 골드 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고 시청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -724,25 +724,25 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
         <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
         <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/04. Bakery Factory/ItemData.xlsx
+++ b/Assets/04. Bakery Factory/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2FDCB8-A8AC-414A-9A95-E2CA467E5770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE19408C-95E3-4CBD-A539-611807D5A905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{FA01C06C-13EC-4B2C-B216-770647FE3958}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -99,19 +100,11 @@
     <t>ItemPrice</t>
   </si>
   <si>
-    <t>5억</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3억</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>50만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -144,47 +137,55 @@
     <t>UpgradeAnvil</t>
   </si>
   <si>
-    <t>500만(최초)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>해머 강화</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>EnhanceHammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeHammer</t>
+  </si>
+  <si>
+    <t>광고를 보고 골드를 획득합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdsGold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TODO : 획득할 골드 표시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고 시청</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>망치를 강화합니다.
-강화 성공확률이 5% 상승합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnhanceHammer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>700만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeHammer</t>
-  </si>
-  <si>
-    <t>광고를 보고 골드를 획득합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AdsGold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODO : 획득할 골드 표시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광고 시청</t>
+강화 성공확률이 3.5% 상승합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000만 * 해머 레벨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500만 * 모루 레벨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000만</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100만</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -231,12 +232,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -552,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B500EC6A-A8F3-4551-A746-C98FD2D2177C}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.25" customWidth="1"/>
@@ -562,9 +566,10 @@
     <col min="5" max="5" width="10.875" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="23.625" customWidth="1"/>
+    <col min="8" max="8" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -584,7 +589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -595,19 +600,24 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2">
         <v>500000</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="H2" t="str">
+        <f>IF(E2&gt;=100000000,ROUND(E2/100000000,0)&amp;"억",
+   ROUND(E2/10000,0)&amp;"만")</f>
+        <v>50만</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -618,19 +628,24 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3">
-        <v>10000000</v>
+        <v>22</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1000000</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H8" si="0">IF(E3&gt;=100000000,ROUND(E3/100000000,0)&amp;"억",
+   ROUND(E3/10000,0)&amp;"만")</f>
+        <v>100만</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -641,19 +656,23 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4">
-        <v>500000000</v>
+        <v>20</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50000000</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>39</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>5000만</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -664,94 +683,111 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2">
         <v>300000000</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>3억</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
       </c>
       <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>500만</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
-      <c r="E6">
-        <v>5000000</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7">
-        <v>7000000</v>
+        <v>29</v>
+      </c>
+      <c r="E7" s="2">
+        <v>30000000</v>
       </c>
       <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>3000만</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="G7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>40</v>
-      </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C8" t="b">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>34</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>0만</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C8" xr:uid="{9F8A1CA2-7F49-4A75-B45F-16D03AE7A658}">
       <formula1>"true, false"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/04. Bakery Factory/ItemData.xlsx
+++ b/Assets/04. Bakery Factory/ItemData.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Unity Project\EnhancingTheSword\Assets\04. Bakery Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE19408C-95E3-4CBD-A539-611807D5A905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7FEDDF-C907-45AC-B3C2-8B8ADEA86504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="5040" windowWidth="28800" windowHeight="15435" xr2:uid="{FA01C06C-13EC-4B2C-B216-770647FE3958}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{FA01C06C-13EC-4B2C-B216-770647FE3958}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>ItemName</t>
   </si>
@@ -53,10 +52,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>레벨 8 이하의 무기에 사용할 수 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -69,14 +64,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>레벨 15 이하의 무기에 사용할 수 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레벨 20 이하의 무기에 사용할 수 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>강화 확률 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -100,14 +87,6 @@
     <t>ItemPrice</t>
   </si>
   <si>
-    <t>3억</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HighGrade AD</t>
   </si>
   <si>
@@ -121,71 +100,117 @@
   </si>
   <si>
     <t>모루 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnhancecAnvil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeAnvil</t>
+  </si>
+  <si>
+    <t>해머 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnhanceHammer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeHammer</t>
+  </si>
+  <si>
+    <t>광고를 보고 골드를 획득합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdsGold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광고 시청</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>모루를 강화합니다.
 강화 단계 한도가 4만큼 증가하고
-무기 강화 확률이 1%p 상승합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnhancecAnvil</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeAnvil</t>
-  </si>
-  <si>
-    <t>해머 강화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnhanceHammer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeHammer</t>
-  </si>
-  <si>
-    <t>광고를 보고 골드를 획득합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Coin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AdsGold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TODO : 획득할 골드 표시</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광고 시청</t>
+무기 강화 확률이 3%p 상승합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품질이 높아보이지 않습니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마나 호응력이 아주 높은 금속입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MIron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mgold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MWhiteGold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마나의 잔념</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법 공학으로 대상이 파괴되었을 때
+되돌릴 수 있는 잔념의 덩어리입니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mmana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법공학의 기초가 되는 재료입니다.
+마도체로 무기의 마나 회로로 사용됩니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>망치를 강화합니다.
-강화 성공확률이 3.5% 상승합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3000만 * 해머 레벨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>500만 * 모루 레벨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5000만</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100만</t>
+무기 강화 확률이 3.5%p 상승하고
+강화 비용이 5% 감소합니다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 8 이하의 무기에 사용할 수 있습니다.
+이번 무기 강화에서 파괴를 방지합니다. (1회)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 15 이하의 무기에 사용할 수 있습니다.
+이번 무기 강화에서 파괴를 방지합니다. (1회)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨 20 이하의 무기에 사용할 수 있습니다.
+이번 무기 강화에서 파괴를 방지합니다. (1회)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -556,25 +581,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B500EC6A-A8F3-4551-A746-C98FD2D2177C}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.25" customWidth="1"/>
-    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="2" max="2" width="49" customWidth="1"/>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="17.75" customWidth="1"/>
     <col min="5" max="5" width="10.875" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
-    <col min="7" max="7" width="23.625" customWidth="1"/>
-    <col min="8" max="8" width="11.375" customWidth="1"/>
+    <col min="7" max="7" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -583,207 +607,284 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E2" s="2">
         <v>500000</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="str">
-        <f>IF(E2&gt;=100000000,ROUND(E2/100000000,0)&amp;"억",
-   ROUND(E2/10000,0)&amp;"만")</f>
+        <v>10</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IF(E2=0,"0",
+   IF(E2&gt;=100000000,
+      INT(E2/100000000)&amp;"억"&amp;
+      IF(INT(MOD(E2,100000000)/10000)&lt;&gt;0," "&amp;INT(MOD(E2,100000000)/10000)&amp;"만","")&amp;
+      IF(MOD(E2,10000)&lt;&gt;0," "&amp;MOD(E2,10000),""),
+      IF(INT(E2/10000)&lt;&gt;0,INT(E2/10000)&amp;"만","")&amp;
+      IF(MOD(E2,10000)&lt;&gt;0," "&amp;MOD(E2,10000),"")
+   )
+)</f>
         <v>50만</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2">
         <v>1000000</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H8" si="0">IF(E3&gt;=100000000,ROUND(E3/100000000,0)&amp;"억",
-   ROUND(E3/10000,0)&amp;"만")</f>
+        <v>11</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" ref="G3:G12" si="0">IF(E3=0,"0",
+   IF(E3&gt;=100000000,
+      INT(E3/100000000)&amp;"억"&amp;
+      IF(INT(MOD(E3,100000000)/10000)&lt;&gt;0," "&amp;INT(MOD(E3,100000000)/10000)&amp;"만","")&amp;
+      IF(MOD(E3,10000)&lt;&gt;0," "&amp;MOD(E3,10000),""),
+      IF(INT(E3/10000)&lt;&gt;0,INT(E3/10000)&amp;"만","")&amp;
+      IF(MOD(E3,10000)&lt;&gt;0," "&amp;MOD(E3,10000),"")
+   )
+)</f>
         <v>100만</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2">
-        <v>50000000</v>
+        <v>30000000</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" t="str">
+        <v>12</v>
+      </c>
+      <c r="G4" t="str">
         <f t="shared" si="0"/>
-        <v>5000만</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3000만</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2">
         <v>300000000</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="str">
+        <v>13</v>
+      </c>
+      <c r="G5" t="str">
         <f t="shared" si="0"/>
         <v>3억</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6" t="b">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2">
         <v>5000000</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" t="str">
+        <v>21</v>
+      </c>
+      <c r="G6" t="str">
         <f t="shared" si="0"/>
         <v>500만</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2">
         <v>30000000</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="str">
+        <v>24</v>
+      </c>
+      <c r="G7" t="str">
         <f t="shared" si="0"/>
         <v>3000만</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E9" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> 3000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="B10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2">
+        <v>50000</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>5만</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="G8" t="s">
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="H8" t="str">
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G11" t="str">
         <f t="shared" si="0"/>
-        <v>0만</v>
+        <v>100만</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C8" xr:uid="{9F8A1CA2-7F49-4A75-B45F-16D03AE7A658}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C12" xr:uid="{9F8A1CA2-7F49-4A75-B45F-16D03AE7A658}">
       <formula1>"true, false"</formula1>
     </dataValidation>
   </dataValidations>
